--- a/ig/StructureDefinition-as-location.xlsx
+++ b/ig/StructureDefinition-as-location.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="420">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:12:51+00:00</t>
+    <t>2024-04-10T13:25:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Location</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>.Role[classCode=SDLC]</t>
@@ -310,318 +310,344 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Location.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Location.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Location.meta.extension:as-ext-data-trace</t>
+  </si>
+  <si>
+    <t>as-ext-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
+</t>
+  </si>
+  <si>
+    <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
+  </si>
+  <si>
+    <t>Location.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Location.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Location.meta.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Location.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Location.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>Location.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Location.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Location.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Location.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Location.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Location.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Location.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Location.extension:usePeriod</t>
+  </si>
+  <si>
+    <t>usePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-use-period}
+</t>
+  </si>
+  <si>
+    <t>FR Core Use Period Extension</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Location.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Location.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Location.meta.extension:as-ext-data-trace</t>
-  </si>
-  <si>
-    <t>as-ext-data-trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
-</t>
-  </si>
-  <si>
-    <t>DataTrace : Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI).</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour tracer l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI)). Des études complémentaires vont être initiées pour envisager l'usage de la ressource Provenance ou meta.source</t>
-  </si>
-  <si>
-    <t>Location.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Location.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Location.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Location.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Location.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Location.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Location.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Location.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Location.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Location.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>Location.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
     <t>Location.modifierExtension</t>
   </si>
   <si>
@@ -645,7 +671,7 @@
 </t>
   </si>
   <si>
-    <t>Unique code or number identifying the location to its users</t>
+    <t>Identifiant fonctionnel du lieu. Il est recommandé de remplir ce champs pour faciliter l'identification des ressources.</t>
   </si>
   <si>
     <t>Unique code or number identifying the location to its users.</t>
@@ -660,6 +686,153 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>Location.identifier.id</t>
+  </si>
+  <si>
+    <t>Location.identifier.extension</t>
+  </si>
+  <si>
+    <t>Location.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Location.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>Location.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Location.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Location.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Location.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>Location.status</t>
   </si>
   <si>
@@ -669,12 +842,6 @@
     <t>The status property covers the general availability of the resource, not the current value which may be covered by the operationStatus, or by a schedule/slots if they are configured for the location.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Indicates whether the location is still in use.</t>
   </si>
   <si>
@@ -694,9 +861,6 @@
   </si>
   <si>
     <t>The operational status covers operation values most relevant to beds (but can also apply to rooms/units/chairs/etc. such as an isolation unit/dialysis chair). This typically covers concepts such as contamination, housekeeping, and other activities like maintenance.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
   </si>
   <si>
     <t>The operational status if the location (where typically a bed/room).</t>
@@ -778,43 +942,36 @@
     <t>Location.type</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t>Type of function performed</t>
+  </si>
+  <si>
+    <t>Indicates the type of function performed at the location.</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>Location.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
-    <t>Type of function performed</t>
-  </si>
-  <si>
-    <t>Indicates the type of function performed at the location.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>Location.telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint
-</t>
-  </si>
-  <si>
-    <t>Contact details of the location</t>
-  </si>
-  <si>
-    <t>The contact details of communication devices available at the location. This can include phone numbers, fax numbers, mobile numbers, email addresses and web sites.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>.telecom</t>
+    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
+  </si>
+  <si>
+    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+  </si>
+  <si>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>TEL</t>
   </si>
   <si>
     <t>Location.address</t>
@@ -851,10 +1008,7 @@
     <t>For purposes of showing relevant locations in queries, we need to categorize locations.</t>
   </si>
   <si>
-    <t>Physical form of the location.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -915,9 +1069,6 @@
     <t>Longitude. The value domain and the interpretation are the same as for the text of the longitude element in KML (see notes below).</t>
   </si>
   <si>
-    <t>Do not use an IEEE type floating point type, instead use something that works like a true decimal, with inbuilt precision (e.g. Java BigInteger)</t>
-  </si>
-  <si>
     <t>(RIM Opted not to map the sub-elements of GPS location, is now an OBS)</t>
   </si>
   <si>
@@ -942,49 +1093,137 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t>Organization responsible for provisioning and upkeep</t>
+  </si>
+  <si>
+    <t>The organization responsible for the provisioning and upkeep of the location.</t>
+  </si>
+  <si>
+    <t>This can also be used as the part of the organization hierarchy where this location provides services. These services can be defined through the HealthcareService resource.</t>
+  </si>
+  <si>
+    <t>Need to know who manages the location.</t>
+  </si>
+  <si>
+    <t>.scopingEntity[classCode=ORG determinerKind=INSTANCE]</t>
+  </si>
+  <si>
+    <t>Location.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
 </t>
   </si>
   <si>
-    <t>Organization responsible for provisioning and upkeep</t>
-  </si>
-  <si>
-    <t>The organization responsible for the provisioning and upkeep of the location.</t>
-  </si>
-  <si>
-    <t>This can also be used as the part of the organization hierarchy where this location provides services. These services can be defined through the HealthcareService resource.</t>
-  </si>
-  <si>
-    <t>Need to know who manages the location.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>.scopingEntity[classCode=ORG determinerKind=INSTANCE]</t>
-  </si>
-  <si>
-    <t>Location.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
+    <t>Another Location this one is physically a part of</t>
+  </si>
+  <si>
+    <t>Another Location of which this Location is physically a part of.</t>
+  </si>
+  <si>
+    <t>For purposes of location, display and identification, knowing which locations are located within other locations is important.</t>
+  </si>
+  <si>
+    <t>.inboundLink[typeCode=PART].source[classCode=SDLC]</t>
+  </si>
+  <si>
+    <t>Location.partOf.id</t>
+  </si>
+  <si>
+    <t>Location.partOf.extension</t>
+  </si>
+  <si>
+    <t>Location.partOf.extension:positionRoom</t>
+  </si>
+  <si>
+    <t>positionRoom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location-position-room}
 </t>
   </si>
   <si>
-    <t>Another Location this one is physically a part of</t>
-  </si>
-  <si>
-    <t>Another Location of which this Location is physically a part of.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>For purposes of location, display and identification, knowing which locations are located within other locations is important.</t>
-  </si>
-  <si>
-    <t>.inboundLink[typeCode=PART].source[classCode=SDLC]</t>
+    <t>FR Core Location Part Of Position Room Extension</t>
+  </si>
+  <si>
+    <t>Position of the bed in the bedroom | Position du lit dans la chambre</t>
+  </si>
+  <si>
+    <t>Location.partOf.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Location.partOf.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Location.partOf.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Location.partOf.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>Location.hoursOfOperation</t>
@@ -1085,9 +1324,6 @@
   </si>
   <si>
     <t>Organizations may have different systems at different locations that provide various services and need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL49"/>
+  <dimension ref="A1:AL66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.98046875" customWidth="true" bestFit="true"/>
@@ -1426,13 +1662,13 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.8203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1442,7 +1678,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="70.30078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1870,13 +2106,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>75</v>
@@ -1884,10 +2120,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1910,13 +2146,13 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1967,7 +2203,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -1982,7 +2218,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>75</v>
@@ -1990,14 +2226,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2016,16 +2252,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2063,19 +2299,19 @@
         <v>75</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2084,13 +2320,13 @@
         <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>75</v>
@@ -2098,13 +2334,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>75</v>
@@ -2126,13 +2362,13 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2183,7 +2419,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2192,10 +2428,10 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -2206,10 +2442,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2235,13 +2471,13 @@
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2291,7 +2527,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2300,13 +2536,13 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ8" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK8" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -2314,10 +2550,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2340,16 +2576,16 @@
         <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2399,7 +2635,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2408,13 +2644,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -2422,10 +2658,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2448,16 +2684,16 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2507,7 +2743,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2516,13 +2752,13 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK10" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -2530,10 +2766,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2556,16 +2792,16 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2603,16 +2839,16 @@
         <v>75</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>143</v>
@@ -2624,13 +2860,13 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>75</v>
@@ -2641,9 +2877,11 @@
         <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>75</v>
       </c>
@@ -2652,7 +2890,7 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>75</v>
@@ -2664,16 +2902,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2684,7 +2922,7 @@
         <v>75</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>75</v>
@@ -2699,13 +2937,13 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -2723,7 +2961,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2732,13 +2970,13 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>75</v>
@@ -2746,10 +2984,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2772,16 +3010,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2807,13 +3045,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2831,7 +3069,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2840,13 +3078,13 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>75</v>
@@ -2854,10 +3092,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2868,28 +3106,28 @@
         <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2915,13 +3153,13 @@
         <v>75</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>75</v>
@@ -2939,22 +3177,22 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>75</v>
@@ -2962,10 +3200,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2982,22 +3220,22 @@
         <v>75</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3023,13 +3261,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -3047,7 +3285,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3056,13 +3294,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>75</v>
@@ -3070,14 +3308,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3096,16 +3334,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3131,13 +3369,13 @@
         <v>75</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>75</v>
@@ -3155,7 +3393,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3164,13 +3402,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -3178,21 +3416,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>75</v>
@@ -3204,16 +3442,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3263,22 +3501,22 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3286,14 +3524,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3312,16 +3550,16 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3359,19 +3597,19 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3380,13 +3618,13 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3394,14 +3632,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3414,26 +3652,22 @@
         <v>75</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>197</v>
-      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
       </c>
@@ -3469,19 +3703,17 @@
         <v>75</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC19" s="2"/>
+      <c r="AD19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC19" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3490,13 +3722,13 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>75</v>
@@ -3504,12 +3736,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>75</v>
       </c>
@@ -3518,7 +3752,7 @@
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>75</v>
@@ -3527,21 +3761,19 @@
         <v>75</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
       </c>
@@ -3589,7 +3821,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3598,35 +3830,35 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>96</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>205</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -3635,21 +3867,23 @@
         <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>75</v>
       </c>
@@ -3673,13 +3907,13 @@
         <v>75</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
@@ -3703,27 +3937,27 @@
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3734,7 +3968,7 @@
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>75</v>
@@ -3746,18 +3980,18 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>75</v>
       </c>
@@ -3781,13 +4015,13 @@
         <v>75</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>219</v>
+        <v>75</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>75</v>
@@ -3805,33 +4039,33 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK22" t="s" s="2">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3851,20 +4085,18 @@
         <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -3913,7 +4145,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>101</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3922,13 +4154,13 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>225</v>
+        <v>102</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -3936,14 +4168,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3962,20 +4194,18 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>107</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>75</v>
       </c>
@@ -4011,19 +4241,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4032,13 +4262,13 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>225</v>
+        <v>102</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4046,10 +4276,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4066,25 +4296,25 @@
         <v>75</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4109,13 +4339,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>75</v>
+        <v>221</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4133,7 +4363,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4142,13 +4372,13 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK25" t="s" s="2">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>75</v>
@@ -4156,10 +4386,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4167,7 +4397,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>84</v>
@@ -4182,19 +4412,19 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4219,13 +4449,11 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -4243,7 +4471,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4252,24 +4480,24 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK26" t="s" s="2">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>243</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4277,10 +4505,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -4292,18 +4520,20 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -4315,7 +4545,7 @@
         <v>75</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>75</v>
@@ -4327,13 +4557,13 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>249</v>
+        <v>75</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -4351,33 +4581,33 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK27" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4385,10 +4615,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>75</v>
@@ -4397,18 +4627,20 @@
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>252</v>
+        <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4421,7 +4653,7 @@
         <v>75</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>75</v>
@@ -4457,22 +4689,22 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>75</v>
@@ -4480,10 +4712,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4503,23 +4735,19 @@
         <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -4567,7 +4795,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4576,13 +4804,13 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4590,10 +4818,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4616,20 +4844,18 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
       </c>
@@ -4653,13 +4879,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>268</v>
+        <v>75</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -4677,7 +4903,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4686,24 +4912,24 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK30" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>243</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4720,24 +4946,22 @@
         <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
@@ -4761,13 +4985,13 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>75</v>
+        <v>221</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>75</v>
+        <v>265</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -4785,7 +5009,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4794,24 +5018,24 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK31" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>75</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4831,16 +5055,16 @@
         <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>101</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>102</v>
+        <v>271</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4867,13 +5091,13 @@
         <v>75</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
@@ -4891,7 +5115,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>103</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4903,32 +5127,32 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>75</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
@@ -4937,19 +5161,19 @@
         <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>108</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>109</v>
+        <v>276</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>110</v>
+        <v>277</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4987,34 +5211,34 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>114</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>98</v>
+        <v>278</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>75</v>
@@ -5029,7 +5253,7 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5042,25 +5266,25 @@
         <v>75</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>110</v>
-      </c>
       <c r="O34" t="s" s="2">
-        <v>197</v>
+        <v>283</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5109,7 +5333,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5118,13 +5342,13 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AK34" t="s" s="2">
-        <v>98</v>
+        <v>278</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5143,7 +5367,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>84</v>
@@ -5155,21 +5379,21 @@
         <v>75</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
       </c>
@@ -5220,19 +5444,19 @@
         <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK35" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5240,10 +5464,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5251,7 +5475,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>84</v>
@@ -5263,21 +5487,23 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
@@ -5301,13 +5527,13 @@
         <v>75</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>75</v>
+        <v>221</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>75</v>
+        <v>294</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5325,33 +5551,33 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK36" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5371,20 +5597,18 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>285</v>
+        <v>227</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5409,13 +5633,11 @@
         <v>75</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>75</v>
@@ -5433,33 +5655,33 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK37" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>75</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5470,7 +5692,7 @@
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -5479,23 +5701,19 @@
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -5543,22 +5761,22 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>96</v>
+        <v>201</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5566,10 +5784,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5592,19 +5810,19 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5653,7 +5871,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5662,13 +5880,13 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AK39" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5676,10 +5894,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5690,7 +5908,7 @@
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
@@ -5699,21 +5917,21 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -5737,13 +5955,11 @@
         <v>75</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>75</v>
+        <v>319</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>75</v>
@@ -5761,33 +5977,33 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ40" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK40" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>75</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5810,16 +6026,18 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>100</v>
+        <v>322</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>101</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>102</v>
+        <v>324</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -5867,7 +6085,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>103</v>
+        <v>321</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5879,10 +6097,10 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>104</v>
+        <v>326</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -5890,21 +6108,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -5916,17 +6134,15 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -5963,34 +6179,34 @@
         <v>75</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -5998,14 +6214,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>280</v>
+        <v>104</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6018,26 +6234,24 @@
         <v>75</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="N43" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
       </c>
@@ -6085,7 +6299,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>283</v>
+        <v>112</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6094,13 +6308,13 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6108,14 +6322,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>75</v>
+        <v>330</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6128,24 +6342,26 @@
         <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
@@ -6169,13 +6385,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>322</v>
+        <v>75</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>323</v>
+        <v>75</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -6193,7 +6409,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6202,13 +6418,13 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>315</v>
+        <v>192</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6216,10 +6432,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6227,7 +6443,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>84</v>
@@ -6242,13 +6458,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6299,22 +6515,22 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK45" t="s" s="2">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6322,10 +6538,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6333,7 +6549,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>84</v>
@@ -6348,13 +6564,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6405,22 +6621,22 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK46" t="s" s="2">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6428,10 +6644,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6454,13 +6670,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6511,7 +6727,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6520,13 +6736,13 @@
         <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK47" t="s" s="2">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6534,10 +6750,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6557,21 +6773,23 @@
         <v>75</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>100</v>
+        <v>256</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
       </c>
@@ -6619,7 +6837,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6628,13 +6846,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK48" t="s" s="2">
-        <v>104</v>
+        <v>350</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6642,10 +6860,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6656,7 +6874,7 @@
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -6668,19 +6886,17 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -6729,29 +6945,1853 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="AI49" t="s" s="2">
+      <c r="H51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AK53" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL49">
+  <autoFilter ref="A1:AL66">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6761,7 +8801,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/StructureDefinition-as-location.xlsx
+++ b/ig/StructureDefinition-as-location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T13:25:16+00:00</t>
+    <t>2024-04-25T11:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/StructureDefinition-as-location.xlsx
+++ b/ig/StructureDefinition-as-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T11:50:43+00:00</t>
+    <t>2024-04-26T07:42:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
